--- a/Emergency_Fund_Calculator.xlsx
+++ b/Emergency_Fund_Calculator.xlsx
@@ -1352,7 +1352,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1" password="CE4B"/>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1" password="8A04"/>
   <mergeCells count="31">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="E10:G10"/>
